--- a/data/trans_orig/P15A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P15A-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2007</t>
+          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23991</t>
+          <t>23362</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47058</t>
+          <t>47032</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5707</t>
+          <t>5702</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18309</t>
+          <t>18289</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33219</t>
+          <t>32697</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59375</t>
+          <t>59306</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>447006</t>
+          <t>447032</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>470073</t>
+          <t>470702</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>449180</t>
+          <t>449200</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>461782</t>
+          <t>461787</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>902178</t>
+          <t>902247</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>928334</t>
+          <t>928856</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,6%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24905</t>
+          <t>24058</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48566</t>
+          <t>49195</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10731</t>
+          <t>10796</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29295</t>
+          <t>29337</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39993</t>
+          <t>40031</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>68961</t>
+          <t>70330</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>686923</t>
+          <t>686294</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>710584</t>
+          <t>711431</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>596199</t>
+          <t>596157</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>614763</t>
+          <t>614698</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1292021</t>
+          <t>1290652</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1320989</t>
+          <t>1320951</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8617</t>
+          <t>8397</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23200</t>
+          <t>24849</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7686</t>
+          <t>7627</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22457</t>
+          <t>22268</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18477</t>
+          <t>20289</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40424</t>
+          <t>43602</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>615468</t>
+          <t>613819</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>630051</t>
+          <t>630271</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>667287</t>
+          <t>667476</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>682058</t>
+          <t>682117</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1287988</t>
+          <t>1284810</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1309935</t>
+          <t>1308123</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12270</t>
+          <t>11628</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29441</t>
+          <t>29923</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4315</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17520</t>
+          <t>18307</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20163</t>
+          <t>19403</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41959</t>
+          <t>42011</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>489706</t>
+          <t>489224</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>506877</t>
+          <t>507519</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>498122</t>
+          <t>497335</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>511327</t>
+          <t>510628</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>992830</t>
+          <t>992778</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1014626</t>
+          <t>1015386</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,12%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4634</t>
+          <t>4572</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18050</t>
+          <t>17783</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4963</t>
+          <t>4940</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17730</t>
+          <t>17419</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11848</t>
+          <t>12115</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29174</t>
+          <t>30941</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>368660</t>
+          <t>368927</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>382076</t>
+          <t>382138</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>386256</t>
+          <t>386567</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>399023</t>
+          <t>399046</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>761522</t>
+          <t>759755</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>778848</t>
+          <t>778581</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1688</t>
+          <t>1761</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9874</t>
+          <t>10074</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5233</t>
+          <t>4665</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17108</t>
+          <t>16587</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7445</t>
+          <t>8030</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22460</t>
+          <t>21805</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>282709</t>
+          <t>282509</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>290895</t>
+          <t>290822</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>325826</t>
+          <t>326347</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>337701</t>
+          <t>338269</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>613057</t>
+          <t>613712</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>628072</t>
+          <t>627487</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2599</t>
+          <t>2359</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12755</t>
+          <t>12075</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14536</t>
+          <t>13833</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33998</t>
+          <t>32433</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19320</t>
+          <t>18993</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>39577</t>
+          <t>41511</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>197128</t>
+          <t>197808</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>207284</t>
+          <t>207524</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>299910</t>
+          <t>301475</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>319372</t>
+          <t>320075</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>504214</t>
+          <t>502280</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>524471</t>
+          <t>524798</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,51%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>102111</t>
+          <t>103130</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>144855</t>
+          <t>147090</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>75288</t>
+          <t>75267</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>115059</t>
+          <t>116065</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>189848</t>
+          <t>190759</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>251213</t>
+          <t>249424</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3131688</t>
+          <t>3129453</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3174432</t>
+          <t>3173413</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3264138</t>
+          <t>3263132</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3303909</t>
+          <t>3303930</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6404528</t>
+          <t>6406317</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6465893</t>
+          <t>6464982</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,13%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2012</t>
+          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13612</t>
+          <t>13790</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31027</t>
+          <t>31941</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4117</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15740</t>
+          <t>16705</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20196</t>
+          <t>20590</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42320</t>
+          <t>41231</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>423119</t>
+          <t>422205</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>440534</t>
+          <t>440356</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>414490</t>
+          <t>413525</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>426113</t>
+          <t>425980</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>842056</t>
+          <t>843145</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>864180</t>
+          <t>863786</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,67%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23384</t>
+          <t>22891</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47479</t>
+          <t>48848</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6136</t>
+          <t>6443</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22952</t>
+          <t>22447</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33312</t>
+          <t>33160</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61279</t>
+          <t>61632</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>639608</t>
+          <t>638239</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>663703</t>
+          <t>664196</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>587303</t>
+          <t>587808</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>604119</t>
+          <t>603812</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1236063</t>
+          <t>1235710</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1264030</t>
+          <t>1264182</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,44%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>8611</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26305</t>
+          <t>27098</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6537</t>
+          <t>5745</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20085</t>
+          <t>19979</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17783</t>
+          <t>18134</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39440</t>
+          <t>39916</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>655558</t>
+          <t>654765</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>672838</t>
+          <t>673252</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>690765</t>
+          <t>690871</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>704313</t>
+          <t>705105</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1353272</t>
+          <t>1352796</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1374929</t>
+          <t>1374578</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3962</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15537</t>
+          <t>15376</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11836</t>
+          <t>11676</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30946</t>
+          <t>30536</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18696</t>
+          <t>17249</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39586</t>
+          <t>39260</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>599080</t>
+          <t>599241</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>610655</t>
+          <t>610628</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>585253</t>
+          <t>585663</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>604363</t>
+          <t>604523</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1191230</t>
+          <t>1191556</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1212120</t>
+          <t>1213567</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,6%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1112</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10965</t>
+          <t>10396</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7547</t>
+          <t>7552</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23244</t>
+          <t>22722</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10708</t>
+          <t>10884</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27611</t>
+          <t>28289</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>418464</t>
+          <t>419033</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>428317</t>
+          <t>428348</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>424556</t>
+          <t>425078</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>440253</t>
+          <t>440248</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>849618</t>
+          <t>848940</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>866521</t>
+          <t>866345</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3921</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14800</t>
+          <t>14347</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6882</t>
+          <t>7019</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21036</t>
+          <t>19913</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13585</t>
+          <t>13783</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31028</t>
+          <t>32298</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>294986</t>
+          <t>295439</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>305865</t>
+          <t>305863</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>332960</t>
+          <t>334083</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>347114</t>
+          <t>346977</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>632754</t>
+          <t>631484</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>650197</t>
+          <t>649999</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,92%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3965</t>
+          <t>4136</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15801</t>
+          <t>16530</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11305</t>
+          <t>11577</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29107</t>
+          <t>30444</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18577</t>
+          <t>17920</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>39570</t>
+          <t>39089</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>234050</t>
+          <t>233321</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>245886</t>
+          <t>245715</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>359872</t>
+          <t>358535</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>377674</t>
+          <t>377402</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>599260</t>
+          <t>599741</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>620253</t>
+          <t>620910</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,19%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>80016</t>
+          <t>80175</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>122151</t>
+          <t>120595</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>79889</t>
+          <t>78736</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>120306</t>
+          <t>119152</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>167014</t>
+          <t>169870</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>226559</t>
+          <t>228695</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3304628</t>
+          <t>3306184</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3346763</t>
+          <t>3346604</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3438003</t>
+          <t>3439157</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3478420</t>
+          <t>3479573</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6758529</t>
+          <t>6756393</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6818074</t>
+          <t>6815218</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,57%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2016</t>
+          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10055</t>
+          <t>9735</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26440</t>
+          <t>26962</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1959</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11778</t>
+          <t>11411</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14291</t>
+          <t>14413</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32901</t>
+          <t>33876</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>393023</t>
+          <t>392501</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>409408</t>
+          <t>409728</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>383977</t>
+          <t>384344</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>393796</t>
+          <t>393805</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>782317</t>
+          <t>781342</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>800927</t>
+          <t>800805</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,23%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14395</t>
+          <t>14099</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32963</t>
+          <t>33313</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4412</t>
+          <t>4529</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16606</t>
+          <t>17435</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21638</t>
+          <t>21929</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43545</t>
+          <t>44251</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>557533</t>
+          <t>557183</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>576101</t>
+          <t>576397</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>546938</t>
+          <t>546109</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>559132</t>
+          <t>559015</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1110495</t>
+          <t>1109789</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1132402</t>
+          <t>1132111</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12030</t>
+          <t>11513</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31016</t>
+          <t>30842</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5451</t>
+          <t>5765</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20894</t>
+          <t>21497</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21767</t>
+          <t>20853</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44987</t>
+          <t>43948</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>638081</t>
+          <t>638255</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>657067</t>
+          <t>657584</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>640492</t>
+          <t>639889</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>655935</t>
+          <t>655621</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1285496</t>
+          <t>1286535</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1308716</t>
+          <t>1309630</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,43%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6167</t>
+          <t>6482</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21178</t>
+          <t>21403</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4813</t>
+          <t>4909</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18207</t>
+          <t>18258</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14152</t>
+          <t>14280</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34654</t>
+          <t>35289</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>624870</t>
+          <t>624645</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>639881</t>
+          <t>639566</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>630870</t>
+          <t>630819</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>644264</t>
+          <t>644168</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7888,7 +7888,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1260471</t>
+          <t>1259836</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1280973</t>
+          <t>1280845</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9227</t>
+          <t>10428</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7605</t>
+          <t>7322</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24567</t>
+          <t>23958</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11080</t>
+          <t>11620</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28639</t>
+          <t>30148</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>468691</t>
+          <t>467490</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>476888</t>
+          <t>476882</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>472282</t>
+          <t>472891</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>489244</t>
+          <t>489527</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>946128</t>
+          <t>944619</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>963687</t>
+          <t>963147</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1844</t>
+          <t>1835</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10067</t>
+          <t>10420</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9606</t>
+          <t>8937</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26428</t>
+          <t>25353</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12996</t>
+          <t>13458</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32744</t>
+          <t>33032</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>324263</t>
+          <t>323910</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>332486</t>
+          <t>332495</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>351334</t>
+          <t>352409</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>368156</t>
+          <t>368825</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>679348</t>
+          <t>679060</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>699096</t>
+          <t>698634</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>4056</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14558</t>
+          <t>14453</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12508</t>
+          <t>13401</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33208</t>
+          <t>32927</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19658</t>
+          <t>19859</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>42775</t>
+          <t>43959</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,69%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>242440</t>
+          <t>242545</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>252996</t>
+          <t>252942</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>366961</t>
+          <t>367242</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>387661</t>
+          <t>386768</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>614392</t>
+          <t>613208</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>637509</t>
+          <t>637308</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,98%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>72684</t>
+          <t>71065</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>108185</t>
+          <t>108483</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>71030</t>
+          <t>69056</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>110136</t>
+          <t>107560</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>150790</t>
+          <t>152738</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>205997</t>
+          <t>206076</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3286165</t>
+          <t>3285867</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3321666</t>
+          <t>3323285</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3434406</t>
+          <t>3436982</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3473512</t>
+          <t>3475486</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6732895</t>
+          <t>6732816</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6788102</t>
+          <t>6786154</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9295,7 +9295,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2023</t>
+          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>2034</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21929</t>
+          <t>23767</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2547</t>
+          <t>2438</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21286</t>
+          <t>22228</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6377</t>
+          <t>7428</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34990</t>
+          <t>34686</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>378058</t>
+          <t>376220</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>398120</t>
+          <t>397953</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>291914</t>
+          <t>290972</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>310653</t>
+          <t>310762</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>678197</t>
+          <t>678501</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>706810</t>
+          <t>705759</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>5939</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23704</t>
+          <t>23755</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1758</t>
+          <t>1771</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11736</t>
+          <t>12706</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8762</t>
+          <t>8935</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30858</t>
+          <t>29814</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>399843</t>
+          <t>399792</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>417960</t>
+          <t>417608</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>499768</t>
+          <t>498798</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>509746</t>
+          <t>509733</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>904193</t>
+          <t>905237</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>926289</t>
+          <t>926116</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4992</t>
+          <t>4858</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18676</t>
+          <t>18948</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>5448</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15465</t>
+          <t>15425</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12304</t>
+          <t>12527</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29576</t>
+          <t>29393</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>517662</t>
+          <t>517390</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>531346</t>
+          <t>531480</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>527003</t>
+          <t>527043</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>537258</t>
+          <t>537020</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1049230</t>
+          <t>1049413</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1066502</t>
+          <t>1066279</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>7854</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34863</t>
+          <t>36232</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7087</t>
+          <t>6882</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18429</t>
+          <t>18214</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18462</t>
+          <t>18721</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46968</t>
+          <t>47034</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>852923</t>
+          <t>851554</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>879636</t>
+          <t>879932</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>694452</t>
+          <t>694667</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>705794</t>
+          <t>705999</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1553699</t>
+          <t>1553633</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1582205</t>
+          <t>1581946</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3077</t>
+          <t>2965</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11595</t>
+          <t>12212</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8382</t>
+          <t>8361</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19573</t>
+          <t>18958</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11097,7 +11097,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13159</t>
+          <t>12540</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27253</t>
+          <t>27286</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,7 +11127,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>549639</t>
+          <t>549022</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>558157</t>
+          <t>558269</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>528332</t>
+          <t>528947</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>539523</t>
+          <t>539544</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,7 +11205,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1081886</t>
+          <t>1081853</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1095980</t>
+          <t>1096599</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11245,7 +11245,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3372</t>
+          <t>3219</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12608</t>
+          <t>11016</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6784</t>
+          <t>6823</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28242</t>
+          <t>28595</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11440,7 +11440,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11721</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32910</t>
+          <t>34050</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>355557</t>
+          <t>357149</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>364793</t>
+          <t>364946</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>580126</t>
+          <t>579773</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>601584</t>
+          <t>601545</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>943623</t>
+          <t>942483</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>964812</t>
+          <t>965331</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>5294</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14150</t>
+          <t>13760</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20476</t>
+          <t>20302</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35223</t>
+          <t>35015</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28406</t>
+          <t>28198</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>44670</t>
+          <t>44894</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>268609</t>
+          <t>268999</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>277611</t>
+          <t>277465</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>390608</t>
+          <t>390816</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>405355</t>
+          <t>405529</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>663920</t>
+          <t>663696</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>680184</t>
+          <t>680392</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>54522</t>
+          <t>52714</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>97424</t>
+          <t>97446</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,7 +12086,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>73012</t>
+          <t>71915</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>114774</t>
+          <t>111038</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>134783</t>
+          <t>133759</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>193208</t>
+          <t>191295</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3362393</t>
+          <t>3362371</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3405295</t>
+          <t>3407103</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3547383</t>
+          <t>3551119</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3589145</t>
+          <t>3590242</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6928766</t>
+          <t>6930679</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6987191</t>
+          <t>6988215</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,12%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P15A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P15A-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23362</t>
+          <t>23885</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47032</t>
+          <t>46850</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5702</t>
+          <t>5381</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18289</t>
+          <t>18433</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>32156</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59306</t>
+          <t>57984</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>447032</t>
+          <t>447214</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>470702</t>
+          <t>470179</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>449200</t>
+          <t>449056</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>461787</t>
+          <t>462108</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>902247</t>
+          <t>903569</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>928856</t>
+          <t>929397</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,66%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24058</t>
+          <t>24706</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49195</t>
+          <t>47626</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10796</t>
+          <t>10973</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29337</t>
+          <t>29012</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40031</t>
+          <t>38674</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70330</t>
+          <t>69050</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>686294</t>
+          <t>687863</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>711431</t>
+          <t>710783</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>596157</t>
+          <t>596482</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>614698</t>
+          <t>614521</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1290652</t>
+          <t>1291932</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1320951</t>
+          <t>1322308</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,16%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8397</t>
+          <t>7914</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24849</t>
+          <t>23976</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7627</t>
+          <t>6966</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22268</t>
+          <t>22118</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20289</t>
+          <t>18322</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43602</t>
+          <t>39570</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>613819</t>
+          <t>614692</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>630271</t>
+          <t>630754</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>667476</t>
+          <t>667626</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>682117</t>
+          <t>682778</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1284810</t>
+          <t>1288842</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1308123</t>
+          <t>1310090</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,62%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11628</t>
+          <t>11822</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29923</t>
+          <t>30135</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5014</t>
+          <t>4989</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18307</t>
+          <t>18861</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19403</t>
+          <t>19463</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>42011</t>
+          <t>42456</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>489224</t>
+          <t>489012</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>507519</t>
+          <t>507325</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>497335</t>
+          <t>496781</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>510628</t>
+          <t>510653</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>992778</t>
+          <t>992333</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1015386</t>
+          <t>1015326</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4572</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17783</t>
+          <t>18567</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4940</t>
+          <t>4836</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17419</t>
+          <t>17757</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12115</t>
+          <t>12112</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30941</t>
+          <t>30017</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>368927</t>
+          <t>368143</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>382138</t>
+          <t>381987</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>386567</t>
+          <t>386229</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>399046</t>
+          <t>399150</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>759755</t>
+          <t>760679</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>778581</t>
+          <t>778584</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1761</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10074</t>
+          <t>10325</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4665</t>
+          <t>4463</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16587</t>
+          <t>16494</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8030</t>
+          <t>7526</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21805</t>
+          <t>21811</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>282509</t>
+          <t>282258</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>290822</t>
+          <t>290810</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>326347</t>
+          <t>326440</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>338269</t>
+          <t>338471</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>613712</t>
+          <t>613706</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>627487</t>
+          <t>627991</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2359</t>
+          <t>2521</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12075</t>
+          <t>12831</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13833</t>
+          <t>14555</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32433</t>
+          <t>34539</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18993</t>
+          <t>19578</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>41511</t>
+          <t>41710</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>197808</t>
+          <t>197052</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>207524</t>
+          <t>207362</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>301475</t>
+          <t>299369</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>320075</t>
+          <t>319353</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>502280</t>
+          <t>502081</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>524798</t>
+          <t>524213</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,4%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>103130</t>
+          <t>102848</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>147090</t>
+          <t>146963</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>75267</t>
+          <t>75895</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>116065</t>
+          <t>113942</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>190759</t>
+          <t>190398</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>249424</t>
+          <t>247827</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3129453</t>
+          <t>3129580</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3173413</t>
+          <t>3173695</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3263132</t>
+          <t>3265255</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3303930</t>
+          <t>3303302</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6406317</t>
+          <t>6407914</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6464982</t>
+          <t>6465343</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,14%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13790</t>
+          <t>13099</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31941</t>
+          <t>30683</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4250</t>
+          <t>3893</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16705</t>
+          <t>15708</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20590</t>
+          <t>20791</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41231</t>
+          <t>43379</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>422205</t>
+          <t>423463</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>440356</t>
+          <t>441047</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>413525</t>
+          <t>414522</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>425980</t>
+          <t>426337</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>843145</t>
+          <t>840997</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>863786</t>
+          <t>863585</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,65%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22891</t>
+          <t>23472</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48848</t>
+          <t>48565</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6443</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22447</t>
+          <t>22664</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33160</t>
+          <t>32760</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61632</t>
+          <t>62916</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>638239</t>
+          <t>638522</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>664196</t>
+          <t>663615</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>587808</t>
+          <t>587591</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>603812</t>
+          <t>604134</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1235710</t>
+          <t>1234426</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1264182</t>
+          <t>1264582</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,47%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8611</t>
+          <t>8670</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27098</t>
+          <t>26155</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5745</t>
+          <t>5933</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19979</t>
+          <t>20181</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18134</t>
+          <t>17284</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39916</t>
+          <t>40641</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>654765</t>
+          <t>655708</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>673252</t>
+          <t>673193</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>690871</t>
+          <t>690669</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>705105</t>
+          <t>704917</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1352796</t>
+          <t>1352071</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1374578</t>
+          <t>1375428</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15376</t>
+          <t>15967</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11676</t>
+          <t>11484</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30536</t>
+          <t>30640</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17249</t>
+          <t>18509</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39260</t>
+          <t>39506</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>599241</t>
+          <t>598650</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>610628</t>
+          <t>610615</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>585663</t>
+          <t>585559</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>604523</t>
+          <t>604715</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1191556</t>
+          <t>1191310</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1213567</t>
+          <t>1212307</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,5%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10396</t>
+          <t>10357</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7552</t>
+          <t>7358</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22722</t>
+          <t>22814</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10884</t>
+          <t>10808</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28289</t>
+          <t>27937</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>419033</t>
+          <t>419072</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>428348</t>
+          <t>428341</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>425078</t>
+          <t>424986</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>440248</t>
+          <t>440442</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>848940</t>
+          <t>849292</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>866345</t>
+          <t>866421</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3923</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14347</t>
+          <t>15034</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7019</t>
+          <t>7564</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19913</t>
+          <t>20678</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13783</t>
+          <t>12989</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32298</t>
+          <t>30907</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>295439</t>
+          <t>294752</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>305863</t>
+          <t>305845</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>334083</t>
+          <t>333318</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>346977</t>
+          <t>346432</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>631484</t>
+          <t>632875</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>649999</t>
+          <t>650793</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>98,04%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4136</t>
+          <t>4084</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16530</t>
+          <t>15921</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11577</t>
+          <t>11486</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30444</t>
+          <t>29427</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17920</t>
+          <t>17926</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>39089</t>
+          <t>40014</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>233321</t>
+          <t>233930</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>245715</t>
+          <t>245767</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>358535</t>
+          <t>359552</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>377402</t>
+          <t>377493</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>599741</t>
+          <t>598816</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>620910</t>
+          <t>620904</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>80175</t>
+          <t>78985</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>120595</t>
+          <t>119930</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>78736</t>
+          <t>80274</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>119152</t>
+          <t>120256</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>169870</t>
+          <t>168303</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>228695</t>
+          <t>227313</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3306184</t>
+          <t>3306849</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3346604</t>
+          <t>3347794</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3439157</t>
+          <t>3438053</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3479573</t>
+          <t>3478035</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6756393</t>
+          <t>6757775</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6815218</t>
+          <t>6816785</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,59%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9735</t>
+          <t>10690</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26962</t>
+          <t>26890</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>1938</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11411</t>
+          <t>11229</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14413</t>
+          <t>13560</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33876</t>
+          <t>33706</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>392501</t>
+          <t>392573</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>409728</t>
+          <t>408773</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>384344</t>
+          <t>384526</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>393805</t>
+          <t>393817</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>781342</t>
+          <t>781512</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>800805</t>
+          <t>801658</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,34%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14099</t>
+          <t>14610</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33313</t>
+          <t>32378</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4529</t>
+          <t>4464</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17435</t>
+          <t>17448</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21929</t>
+          <t>22168</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44251</t>
+          <t>43156</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>557183</t>
+          <t>558118</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>576397</t>
+          <t>575886</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>546109</t>
+          <t>546096</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>559015</t>
+          <t>559080</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1109789</t>
+          <t>1110884</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1132111</t>
+          <t>1131872</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,08%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11513</t>
+          <t>12484</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30842</t>
+          <t>31283</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5765</t>
+          <t>5857</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21497</t>
+          <t>20480</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20853</t>
+          <t>20910</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43948</t>
+          <t>43867</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>638255</t>
+          <t>637814</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>657584</t>
+          <t>656613</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>639889</t>
+          <t>640906</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>655621</t>
+          <t>655529</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1286535</t>
+          <t>1286616</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1309630</t>
+          <t>1309573</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6482</t>
+          <t>6423</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21403</t>
+          <t>22414</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4909</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18258</t>
+          <t>19008</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14280</t>
+          <t>13588</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35289</t>
+          <t>33775</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>624645</t>
+          <t>623634</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>639566</t>
+          <t>639625</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>630819</t>
+          <t>630069</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>644168</t>
+          <t>644158</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1259836</t>
+          <t>1261350</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1280845</t>
+          <t>1281537</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10428</t>
+          <t>10107</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7322</t>
+          <t>7270</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23958</t>
+          <t>24319</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11620</t>
+          <t>11383</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30148</t>
+          <t>28575</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>467490</t>
+          <t>467811</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>476882</t>
+          <t>476880</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>472891</t>
+          <t>472530</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>489527</t>
+          <t>489579</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>944619</t>
+          <t>946192</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>963147</t>
+          <t>963384</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1835</t>
+          <t>1757</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10420</t>
+          <t>10356</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8937</t>
+          <t>9543</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25353</t>
+          <t>25468</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13458</t>
+          <t>12674</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>33032</t>
+          <t>31408</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>323910</t>
+          <t>323974</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>332495</t>
+          <t>332573</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>352409</t>
+          <t>352294</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>368825</t>
+          <t>368219</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>679060</t>
+          <t>680684</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>698634</t>
+          <t>699418</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,22%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4056</t>
+          <t>4066</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14453</t>
+          <t>14044</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13401</t>
+          <t>12738</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32927</t>
+          <t>32128</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19859</t>
+          <t>19709</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>43959</t>
+          <t>43649</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>242545</t>
+          <t>242954</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>252942</t>
+          <t>252932</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>367242</t>
+          <t>368041</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>386768</t>
+          <t>387431</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>613208</t>
+          <t>613518</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>637308</t>
+          <t>637458</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,0%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>71065</t>
+          <t>70895</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>108483</t>
+          <t>108804</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>69056</t>
+          <t>69712</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>107560</t>
+          <t>110150</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>152738</t>
+          <t>152632</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>206076</t>
+          <t>205724</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3285867</t>
+          <t>3285546</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3323285</t>
+          <t>3323455</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,7 +9220,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3436982</t>
+          <t>3434392</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3475486</t>
+          <t>3474830</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6732816</t>
+          <t>6733168</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6786154</t>
+          <t>6786260</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,7 +9290,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7814</t>
+          <t>8218</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2034</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23767</t>
+          <t>25750</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8826</t>
+          <t>9401</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2438</t>
+          <t>2295</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22228</t>
+          <t>23406</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,22 +9735,22 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>16640</t>
+          <t>17618</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7428</t>
+          <t>7988</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34686</t>
+          <t>38031</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>392173</t>
+          <t>399575</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>376220</t>
+          <t>382043</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>397953</t>
+          <t>406297</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>304374</t>
+          <t>353111</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>290972</t>
+          <t>339106</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>310762</t>
+          <t>360217</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,27 +9848,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>696547</t>
+          <t>752687</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>678501</t>
+          <t>732274</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>705759</t>
+          <t>762317</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11758</t>
+          <t>15735</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5939</t>
+          <t>7182</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23755</t>
+          <t>28709</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5049</t>
+          <t>5065</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>1821</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12706</t>
+          <t>11227</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>16808</t>
+          <t>20799</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8935</t>
+          <t>12309</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29814</t>
+          <t>34858</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>411789</t>
+          <t>461155</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>399792</t>
+          <t>448181</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>417608</t>
+          <t>469708</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>506455</t>
+          <t>496018</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>498798</t>
+          <t>489856</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>509733</t>
+          <t>499262</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>918243</t>
+          <t>957174</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>905237</t>
+          <t>943115</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>926116</t>
+          <t>965664</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>10172</t>
+          <t>11859</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4858</t>
+          <t>6248</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18948</t>
+          <t>22310</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9319</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5448</t>
+          <t>5820</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15425</t>
+          <t>16162</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>19491</t>
+          <t>22180</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12527</t>
+          <t>14908</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29393</t>
+          <t>33445</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>526166</t>
+          <t>608978</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>517390</t>
+          <t>598527</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>531480</t>
+          <t>614589</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>533149</t>
+          <t>611818</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>527043</t>
+          <t>605977</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>537020</t>
+          <t>616319</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1059315</t>
+          <t>1220796</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1049413</t>
+          <t>1209531</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1066279</t>
+          <t>1228068</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>21618</t>
+          <t>22526</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7854</t>
+          <t>13921</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36232</t>
+          <t>34658</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11668</t>
+          <t>12832</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6882</t>
+          <t>8005</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18214</t>
+          <t>19804</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>33286</t>
+          <t>35358</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18721</t>
+          <t>25366</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47034</t>
+          <t>48941</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>866168</t>
+          <t>678091</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>851554</t>
+          <t>665959</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>879932</t>
+          <t>686696</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>701213</t>
+          <t>724054</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>694667</t>
+          <t>717082</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>705999</t>
+          <t>728881</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1567381</t>
+          <t>1402146</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1553633</t>
+          <t>1388563</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1581946</t>
+          <t>1412138</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,24%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6603</t>
+          <t>7303</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2965</t>
+          <t>3729</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12212</t>
+          <t>14153</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>12916</t>
+          <t>14327</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8361</t>
+          <t>8975</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18958</t>
+          <t>20138</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>19518</t>
+          <t>21630</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12540</t>
+          <t>14738</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27286</t>
+          <t>30127</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>554631</t>
+          <t>602043</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>549022</t>
+          <t>595193</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>558269</t>
+          <t>605617</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>534989</t>
+          <t>594528</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>528947</t>
+          <t>588717</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>539544</t>
+          <t>599880</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1089621</t>
+          <t>1196572</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1081853</t>
+          <t>1188075</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1096599</t>
+          <t>1203464</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>7002</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>3635</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11016</t>
+          <t>12546</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>16762</t>
+          <t>18759</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6823</t>
+          <t>13520</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28595</t>
+          <t>25755</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>23138</t>
+          <t>25761</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11202</t>
+          <t>19087</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>34050</t>
+          <t>33741</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>361789</t>
+          <t>400078</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>357149</t>
+          <t>394534</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>364946</t>
+          <t>403445</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>591606</t>
+          <t>420407</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>579773</t>
+          <t>413411</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>601545</t>
+          <t>425646</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>953395</t>
+          <t>820485</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>942483</t>
+          <t>812505</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>965331</t>
+          <t>827159</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>97,74%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>8589</t>
+          <t>9701</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5294</t>
+          <t>5400</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13760</t>
+          <t>15824</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>26946</t>
+          <t>28734</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20302</t>
+          <t>22103</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35015</t>
+          <t>37248</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>35535</t>
+          <t>38435</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28198</t>
+          <t>30609</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>44894</t>
+          <t>48221</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>274170</t>
+          <t>300497</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>268999</t>
+          <t>294374</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>277465</t>
+          <t>304798</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>398885</t>
+          <t>435875</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>390816</t>
+          <t>427361</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>405529</t>
+          <t>442506</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>673055</t>
+          <t>736372</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>663696</t>
+          <t>726586</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>680392</t>
+          <t>744198</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,05%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>72930</t>
+          <t>82343</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>52714</t>
+          <t>65126</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>97446</t>
+          <t>107011</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,67 +12101,67 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>91486</t>
+          <t>99438</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>71915</t>
+          <t>82827</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>111038</t>
+          <t>119612</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>181781</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>156515</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>211970</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
           <t>2,5%</t>
         </is>
       </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>1,96%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>3,03%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>164416</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>133759</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>191295</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3386887</t>
+          <t>3450419</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3362371</t>
+          <t>3425751</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3407103</t>
+          <t>3467636</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,67 +12214,67 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3570671</t>
+          <t>3635813</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3551119</t>
+          <t>3615639</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3590242</t>
+          <t>3652424</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
+          <t>97,34%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>96,8%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>97,78%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>8503</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>7086232</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>7056043</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>7111498</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
           <t>97,5%</t>
         </is>
       </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>96,97%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>98,04%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>8503</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>6957558</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>6930679</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>6988215</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>97,69%</t>
-        </is>
-      </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>97,85%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3662157</t>
+          <t>3735251</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3662157</t>
+          <t>3735251</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3662157</t>
+          <t>3735251</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7121974</t>
+          <t>7268013</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7121974</t>
+          <t>7268013</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7121974</t>
+          <t>7268013</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
